--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130433109</v>
       </c>
       <c r="B7" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433115</v>
+        <v>130433116</v>
       </c>
       <c r="B8" t="n">
         <v>57823</v>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360725</v>
+        <v>360751</v>
       </c>
       <c r="R8" t="n">
-        <v>6540811</v>
+        <v>6540820</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433116</v>
+        <v>130433115</v>
       </c>
       <c r="B9" t="n">
         <v>57823</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360751</v>
+        <v>360725</v>
       </c>
       <c r="R9" t="n">
-        <v>6540820</v>
+        <v>6540811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
         <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433110</v>
+        <v>130433118</v>
       </c>
       <c r="B12" t="n">
-        <v>111077</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360682</v>
+        <v>360679</v>
       </c>
       <c r="R12" t="n">
-        <v>6540850</v>
+        <v>6540844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,13 +1987,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2014,7 +2033,7 @@
         <v>130433111</v>
       </c>
       <c r="B13" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2127,42 +2146,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433118</v>
+        <v>130433110</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>111080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360679</v>
+        <v>360682</v>
       </c>
       <c r="R14" t="n">
-        <v>6540844</v>
+        <v>6540850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2229,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,32 +2238,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>111077</v>
+        <v>101112</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R15" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>101109</v>
+        <v>111080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R16" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,7 +2497,7 @@
         <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>130433144</v>
       </c>
       <c r="B18" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>130433161</v>
       </c>
       <c r="B19" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>130433108</v>
       </c>
       <c r="B20" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>130433159</v>
       </c>
       <c r="B23" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>130433101</v>
       </c>
       <c r="B24" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>130433105</v>
       </c>
       <c r="B25" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>130433102</v>
       </c>
       <c r="B27" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>130433103</v>
       </c>
       <c r="B35" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>130433160</v>
       </c>
       <c r="B36" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>130433147</v>
       </c>
       <c r="B37" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130433120</v>
       </c>
       <c r="B3" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130433109</v>
       </c>
       <c r="B7" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433116</v>
+        <v>130433115</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360751</v>
+        <v>360725</v>
       </c>
       <c r="R8" t="n">
-        <v>6540820</v>
+        <v>6540811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433115</v>
+        <v>130433116</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360725</v>
+        <v>360751</v>
       </c>
       <c r="R9" t="n">
-        <v>6540811</v>
+        <v>6540820</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B10" t="n">
-        <v>101112</v>
+        <v>111106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R10" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B11" t="n">
-        <v>111080</v>
+        <v>101138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R11" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,7 +1898,7 @@
         <v>130433118</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433111</v>
+        <v>130433110</v>
       </c>
       <c r="B13" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360659</v>
+        <v>360682</v>
       </c>
       <c r="R13" t="n">
-        <v>6540849</v>
+        <v>6540850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433110</v>
+        <v>130433111</v>
       </c>
       <c r="B14" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360682</v>
+        <v>360659</v>
       </c>
       <c r="R14" t="n">
-        <v>6540850</v>
+        <v>6540849</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>101112</v>
+        <v>111106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R15" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>111080</v>
+        <v>101138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R16" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433100</v>
+        <v>130433145</v>
       </c>
       <c r="B17" t="n">
-        <v>111080</v>
+        <v>101138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360646</v>
+        <v>360628</v>
       </c>
       <c r="R17" t="n">
-        <v>6540820</v>
+        <v>6540817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2613,7 +2613,7 @@
         <v>130433144</v>
       </c>
       <c r="B18" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>130433161</v>
       </c>
       <c r="B19" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>130433108</v>
       </c>
       <c r="B20" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433145</v>
+        <v>130433100</v>
       </c>
       <c r="B21" t="n">
-        <v>101112</v>
+        <v>111106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360628</v>
+        <v>360646</v>
       </c>
       <c r="R21" t="n">
-        <v>6540817</v>
+        <v>6540820</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3072,7 +3072,7 @@
         <v>130433098</v>
       </c>
       <c r="B22" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433159</v>
+        <v>130433105</v>
       </c>
       <c r="B23" t="n">
-        <v>101112</v>
+        <v>111106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360652</v>
+        <v>360726</v>
       </c>
       <c r="R23" t="n">
-        <v>6540954</v>
+        <v>6540873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
         <v>130433101</v>
       </c>
       <c r="B24" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433105</v>
+        <v>130433159</v>
       </c>
       <c r="B25" t="n">
-        <v>111080</v>
+        <v>101138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,21 +3440,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360726</v>
+        <v>360652</v>
       </c>
       <c r="R25" t="n">
-        <v>6540873</v>
+        <v>6540954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B26" t="n">
-        <v>101112</v>
+        <v>111106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R26" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,11 +3644,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3666,10 +3661,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433102</v>
+        <v>130433155</v>
       </c>
       <c r="B27" t="n">
-        <v>111080</v>
+        <v>101138</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,21 +3672,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360627</v>
+        <v>360610</v>
       </c>
       <c r="R27" t="n">
-        <v>6540799</v>
+        <v>6540895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,6 +3760,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3785,7 +3785,7 @@
         <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>130433103</v>
       </c>
       <c r="B35" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>130433160</v>
       </c>
       <c r="B36" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>130433147</v>
       </c>
       <c r="B37" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>130433117</v>
       </c>
       <c r="B38" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433145</v>
+        <v>130433108</v>
       </c>
       <c r="B17" t="n">
-        <v>101138</v>
+        <v>111106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360628</v>
+        <v>360696</v>
       </c>
       <c r="R17" t="n">
-        <v>6540817</v>
+        <v>6540881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433144</v>
+        <v>130433100</v>
       </c>
       <c r="B18" t="n">
-        <v>101138</v>
+        <v>111106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360645</v>
+        <v>360646</v>
       </c>
       <c r="R18" t="n">
-        <v>6540823</v>
+        <v>6540820</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,7 +2726,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433161</v>
+        <v>130433144</v>
       </c>
       <c r="B19" t="n">
         <v>101138</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360670</v>
+        <v>360645</v>
       </c>
       <c r="R19" t="n">
-        <v>6540973</v>
+        <v>6540823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2805,6 +2805,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433108</v>
+        <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>111106</v>
+        <v>101138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2880,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360696</v>
+        <v>360670</v>
       </c>
       <c r="R20" t="n">
-        <v>6540881</v>
+        <v>6540973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2916,11 +2921,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433100</v>
+        <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>111106</v>
+        <v>101138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360646</v>
+        <v>360628</v>
       </c>
       <c r="R21" t="n">
-        <v>6540820</v>
+        <v>6540817</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130433109</v>
       </c>
       <c r="B7" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>130433113</v>
       </c>
       <c r="B10" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>130433146</v>
       </c>
       <c r="B11" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>130433110</v>
       </c>
       <c r="B13" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>130433111</v>
       </c>
       <c r="B14" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433108</v>
+        <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360696</v>
+        <v>360646</v>
       </c>
       <c r="R17" t="n">
-        <v>6540881</v>
+        <v>6540820</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433100</v>
+        <v>130433108</v>
       </c>
       <c r="B18" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360646</v>
+        <v>360696</v>
       </c>
       <c r="R18" t="n">
-        <v>6540820</v>
+        <v>6540881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,7 +2729,7 @@
         <v>130433144</v>
       </c>
       <c r="B19" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433105</v>
+        <v>130433101</v>
       </c>
       <c r="B23" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360726</v>
+        <v>360701</v>
       </c>
       <c r="R23" t="n">
-        <v>6540873</v>
+        <v>6540855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3313,10 +3313,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433101</v>
+        <v>130433105</v>
       </c>
       <c r="B24" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360701</v>
+        <v>360726</v>
       </c>
       <c r="R24" t="n">
-        <v>6540855</v>
+        <v>6540873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,7 +3432,7 @@
         <v>130433159</v>
       </c>
       <c r="B25" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433102</v>
+        <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>111106</v>
+        <v>101139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360627</v>
+        <v>360610</v>
       </c>
       <c r="R26" t="n">
-        <v>6540799</v>
+        <v>6540895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,6 +3644,11 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3661,10 +3666,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433155</v>
+        <v>130433149</v>
       </c>
       <c r="B27" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360610</v>
+        <v>360769</v>
       </c>
       <c r="R27" t="n">
-        <v>6540895</v>
+        <v>6540905</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,11 +3765,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433149</v>
+        <v>130433102</v>
       </c>
       <c r="B28" t="n">
-        <v>101138</v>
+        <v>111107</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360769</v>
+        <v>360627</v>
       </c>
       <c r="R28" t="n">
-        <v>6540905</v>
+        <v>6540799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>130433103</v>
       </c>
       <c r="B35" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>130433160</v>
       </c>
       <c r="B36" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>130433147</v>
       </c>
       <c r="B37" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130433120</v>
+        <v>130433151</v>
       </c>
       <c r="B3" t="n">
-        <v>58224</v>
+        <v>101140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,50 +817,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>360722</v>
+        <v>360741</v>
       </c>
       <c r="R3" t="n">
-        <v>6540833</v>
+        <v>6540886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +898,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -929,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130433151</v>
+        <v>130433152</v>
       </c>
       <c r="B4" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -972,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360741</v>
+        <v>360683</v>
       </c>
       <c r="R4" t="n">
-        <v>6540886</v>
+        <v>6540849</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130433152</v>
+        <v>130433143</v>
       </c>
       <c r="B5" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360683</v>
+        <v>360644</v>
       </c>
       <c r="R5" t="n">
-        <v>6540849</v>
+        <v>6540876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkbarrskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130433143</v>
+        <v>130433120</v>
       </c>
       <c r="B6" t="n">
-        <v>101139</v>
+        <v>58224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,42 +1165,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360644</v>
+        <v>360722</v>
       </c>
       <c r="R6" t="n">
-        <v>6540876</v>
+        <v>6540833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1254,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1277,42 +1277,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433109</v>
+        <v>130433116</v>
       </c>
       <c r="B7" t="n">
-        <v>111107</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360689</v>
+        <v>360751</v>
       </c>
       <c r="R7" t="n">
-        <v>6540864</v>
+        <v>6540820</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,13 +1369,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1528,42 +1547,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433116</v>
+        <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>111108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1571,10 +1590,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360751</v>
+        <v>360689</v>
       </c>
       <c r="R9" t="n">
-        <v>6540820</v>
+        <v>6540864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1630,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,32 +1639,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>111107</v>
+        <v>101140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R10" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>101139</v>
+        <v>111108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R11" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2033,7 +2033,7 @@
         <v>130433110</v>
       </c>
       <c r="B13" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>130433111</v>
       </c>
       <c r="B14" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>111107</v>
+        <v>101140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R15" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>101139</v>
+        <v>111108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R16" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,7 +2497,7 @@
         <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>130433108</v>
       </c>
       <c r="B18" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>130433144</v>
       </c>
       <c r="B19" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>130433101</v>
       </c>
       <c r="B23" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>130433105</v>
       </c>
       <c r="B24" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>130433159</v>
       </c>
       <c r="B25" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>130433149</v>
       </c>
       <c r="B27" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>130433102</v>
       </c>
       <c r="B28" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>130433103</v>
       </c>
       <c r="B35" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>130433160</v>
       </c>
       <c r="B36" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>130433147</v>
       </c>
       <c r="B37" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4952,61 +4952,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B38" t="n">
-        <v>57849</v>
+        <v>101140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R38" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5043,7 +5035,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5052,6 +5044,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5075,53 +5068,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B39" t="n">
-        <v>101139</v>
+        <v>57849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R39" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5167,7 +5168,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130433151</v>
       </c>
       <c r="B3" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>130433152</v>
       </c>
       <c r="B4" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>130433143</v>
       </c>
       <c r="B5" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>130433120</v>
       </c>
       <c r="B6" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433116</v>
+        <v>130433115</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360751</v>
+        <v>360725</v>
       </c>
       <c r="R7" t="n">
-        <v>6540820</v>
+        <v>6540811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433115</v>
+        <v>130433116</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360725</v>
+        <v>360751</v>
       </c>
       <c r="R8" t="n">
-        <v>6540811</v>
+        <v>6540820</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1550,7 +1550,7 @@
         <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B10" t="n">
-        <v>101140</v>
+        <v>111110</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R10" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B11" t="n">
-        <v>111108</v>
+        <v>101142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R11" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433118</v>
+        <v>130433110</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>111110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360679</v>
+        <v>360682</v>
       </c>
       <c r="R12" t="n">
-        <v>6540844</v>
+        <v>6540850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,32 +1987,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2030,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433110</v>
+        <v>130433111</v>
       </c>
       <c r="B13" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360682</v>
+        <v>360659</v>
       </c>
       <c r="R13" t="n">
-        <v>6540850</v>
+        <v>6540849</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,42 +2127,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433111</v>
+        <v>130433118</v>
       </c>
       <c r="B14" t="n">
-        <v>111108</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2189,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360659</v>
+        <v>360679</v>
       </c>
       <c r="R14" t="n">
-        <v>6540849</v>
+        <v>6540844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,13 +2219,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>101140</v>
+        <v>111110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R15" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>111108</v>
+        <v>101142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R16" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,7 +2497,7 @@
         <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>130433108</v>
       </c>
       <c r="B18" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>130433144</v>
       </c>
       <c r="B19" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3069,61 +3069,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130433098</v>
+        <v>130433101</v>
       </c>
       <c r="B22" t="n">
-        <v>58011</v>
+        <v>111110</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>360645</v>
+        <v>360701</v>
       </c>
       <c r="R22" t="n">
-        <v>6540888</v>
+        <v>6540855</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3160,7 +3152,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3169,17 +3161,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3197,10 +3185,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433101</v>
+        <v>130433105</v>
       </c>
       <c r="B23" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360701</v>
+        <v>360726</v>
       </c>
       <c r="R23" t="n">
-        <v>6540855</v>
+        <v>6540873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3268,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3313,10 +3301,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433105</v>
+        <v>130433159</v>
       </c>
       <c r="B24" t="n">
-        <v>111108</v>
+        <v>101142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3324,21 +3312,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3356,10 +3344,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360726</v>
+        <v>360652</v>
       </c>
       <c r="R24" t="n">
-        <v>6540873</v>
+        <v>6540954</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3396,7 +3384,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3411,7 +3399,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3429,53 +3417,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433159</v>
+        <v>130433098</v>
       </c>
       <c r="B25" t="n">
-        <v>101140</v>
+        <v>58013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360652</v>
+        <v>360645</v>
       </c>
       <c r="R25" t="n">
-        <v>6540954</v>
+        <v>6540888</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3508,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3521,13 +3517,17 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B26" t="n">
-        <v>101140</v>
+        <v>111110</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R26" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,11 +3644,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3666,10 +3661,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433149</v>
+        <v>130433155</v>
       </c>
       <c r="B27" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360769</v>
+        <v>360610</v>
       </c>
       <c r="R27" t="n">
-        <v>6540905</v>
+        <v>6540895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,6 +3760,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433102</v>
+        <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>111108</v>
+        <v>101142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360627</v>
+        <v>360769</v>
       </c>
       <c r="R28" t="n">
-        <v>6540799</v>
+        <v>6540905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433103</v>
+        <v>130433160</v>
       </c>
       <c r="B35" t="n">
-        <v>111108</v>
+        <v>101142</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360640</v>
+        <v>360656</v>
       </c>
       <c r="R35" t="n">
-        <v>6540794</v>
+        <v>6540928</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,11 +4688,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4725,10 +4720,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433160</v>
+        <v>130433147</v>
       </c>
       <c r="B36" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,10 +4763,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360656</v>
+        <v>360645</v>
       </c>
       <c r="R36" t="n">
-        <v>6540928</v>
+        <v>6540790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4804,6 +4799,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433147</v>
+        <v>130433103</v>
       </c>
       <c r="B37" t="n">
-        <v>101140</v>
+        <v>111110</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360645</v>
+        <v>360640</v>
       </c>
       <c r="R37" t="n">
-        <v>6540790</v>
+        <v>6540794</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,53 +4952,61 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B38" t="n">
-        <v>101140</v>
+        <v>57851</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R38" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5035,7 +5043,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5044,7 +5052,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5068,61 +5075,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>57849</v>
+        <v>101142</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R39" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5159,7 +5158,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5168,6 +5167,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130433151</v>
+        <v>130433120</v>
       </c>
       <c r="B3" t="n">
-        <v>101142</v>
+        <v>58226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,42 +817,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>360741</v>
+        <v>360722</v>
       </c>
       <c r="R3" t="n">
-        <v>6540886</v>
+        <v>6540833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +906,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130433152</v>
+        <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360683</v>
+        <v>360741</v>
       </c>
       <c r="R4" t="n">
-        <v>6540849</v>
+        <v>6540886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkbarrskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130433143</v>
+        <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360644</v>
+        <v>360683</v>
       </c>
       <c r="R5" t="n">
-        <v>6540876</v>
+        <v>6540849</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130433120</v>
+        <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>58226</v>
+        <v>101146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,50 +1172,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360722</v>
+        <v>360644</v>
       </c>
       <c r="R6" t="n">
-        <v>6540833</v>
+        <v>6540876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,6 +1253,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1412,42 +1412,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433116</v>
+        <v>130433109</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>111114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360751</v>
+        <v>360689</v>
       </c>
       <c r="R8" t="n">
-        <v>6540820</v>
+        <v>6540864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,32 +1504,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1547,42 +1528,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433109</v>
+        <v>130433116</v>
       </c>
       <c r="B9" t="n">
-        <v>111110</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1590,10 +1571,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360689</v>
+        <v>360751</v>
       </c>
       <c r="R9" t="n">
-        <v>6540864</v>
+        <v>6540820</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,7 +1611,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,13 +1620,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>111110</v>
+        <v>101146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R10" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>101142</v>
+        <v>111114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R11" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433110</v>
+        <v>130433118</v>
       </c>
       <c r="B12" t="n">
-        <v>111110</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360682</v>
+        <v>360679</v>
       </c>
       <c r="R12" t="n">
-        <v>6540850</v>
+        <v>6540844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,13 +1987,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,10 +2030,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433111</v>
+        <v>130433110</v>
       </c>
       <c r="B13" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,10 +2073,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360659</v>
+        <v>360682</v>
       </c>
       <c r="R13" t="n">
-        <v>6540849</v>
+        <v>6540850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2127,42 +2146,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433118</v>
+        <v>130433111</v>
       </c>
       <c r="B14" t="n">
-        <v>57851</v>
+        <v>111114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360679</v>
+        <v>360659</v>
       </c>
       <c r="R14" t="n">
-        <v>6540844</v>
+        <v>6540849</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2229,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,32 +2238,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
         <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433108</v>
+        <v>130433144</v>
       </c>
       <c r="B18" t="n">
-        <v>111110</v>
+        <v>101146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360696</v>
+        <v>360645</v>
       </c>
       <c r="R18" t="n">
-        <v>6540881</v>
+        <v>6540823</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,10 +2726,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433144</v>
+        <v>130433161</v>
       </c>
       <c r="B19" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360645</v>
+        <v>360670</v>
       </c>
       <c r="R19" t="n">
-        <v>6540823</v>
+        <v>6540973</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2805,11 +2805,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433161</v>
+        <v>130433108</v>
       </c>
       <c r="B20" t="n">
-        <v>101142</v>
+        <v>111114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,21 +2848,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360670</v>
+        <v>360696</v>
       </c>
       <c r="R20" t="n">
-        <v>6540973</v>
+        <v>6540881</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,6 +2916,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,7 +2956,7 @@
         <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130433101</v>
+        <v>130433159</v>
       </c>
       <c r="B22" t="n">
-        <v>111110</v>
+        <v>101146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,21 +3080,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>360701</v>
+        <v>360652</v>
       </c>
       <c r="R22" t="n">
-        <v>6540855</v>
+        <v>6540954</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433105</v>
+        <v>130433101</v>
       </c>
       <c r="B23" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360726</v>
+        <v>360701</v>
       </c>
       <c r="R23" t="n">
-        <v>6540873</v>
+        <v>6540855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433159</v>
+        <v>130433105</v>
       </c>
       <c r="B24" t="n">
-        <v>101142</v>
+        <v>111114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360652</v>
+        <v>360726</v>
       </c>
       <c r="R24" t="n">
-        <v>6540954</v>
+        <v>6540873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433102</v>
+        <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>111110</v>
+        <v>101146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360627</v>
+        <v>360610</v>
       </c>
       <c r="R26" t="n">
-        <v>6540799</v>
+        <v>6540895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,6 +3644,11 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3661,10 +3666,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B27" t="n">
-        <v>101142</v>
+        <v>111114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,21 +3677,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R27" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,11 +3765,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3785,7 +3785,7 @@
         <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433160</v>
+        <v>130433103</v>
       </c>
       <c r="B35" t="n">
-        <v>101142</v>
+        <v>111114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360656</v>
+        <v>360640</v>
       </c>
       <c r="R35" t="n">
-        <v>6540928</v>
+        <v>6540794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,6 +4688,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4720,10 +4725,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433147</v>
+        <v>130433160</v>
       </c>
       <c r="B36" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4763,10 +4768,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360645</v>
+        <v>360656</v>
       </c>
       <c r="R36" t="n">
-        <v>6540790</v>
+        <v>6540928</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4799,11 +4804,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433103</v>
+        <v>130433147</v>
       </c>
       <c r="B37" t="n">
-        <v>111110</v>
+        <v>101146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360640</v>
+        <v>360645</v>
       </c>
       <c r="R37" t="n">
-        <v>6540794</v>
+        <v>6540790</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,61 +4952,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B38" t="n">
-        <v>57851</v>
+        <v>101146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R38" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5043,7 +5035,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5052,6 +5044,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5075,53 +5068,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B39" t="n">
-        <v>101142</v>
+        <v>57851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R39" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5167,7 +5168,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -1277,42 +1277,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433115</v>
+        <v>130433109</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>111114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360725</v>
+        <v>360689</v>
       </c>
       <c r="R7" t="n">
-        <v>6540811</v>
+        <v>6540864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,32 +1369,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,42 +1393,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433109</v>
+        <v>130433115</v>
       </c>
       <c r="B8" t="n">
-        <v>111114</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1455,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360689</v>
+        <v>360725</v>
       </c>
       <c r="R8" t="n">
-        <v>6540864</v>
+        <v>6540811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,13 +1485,32 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B10" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R10" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B11" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R11" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R15" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R16" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433144</v>
+        <v>130433108</v>
       </c>
       <c r="B18" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360645</v>
+        <v>360696</v>
       </c>
       <c r="R18" t="n">
-        <v>6540823</v>
+        <v>6540881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,7 +2726,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433161</v>
+        <v>130433144</v>
       </c>
       <c r="B19" t="n">
         <v>101146</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360670</v>
+        <v>360645</v>
       </c>
       <c r="R19" t="n">
-        <v>6540973</v>
+        <v>6540823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2805,6 +2805,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433108</v>
+        <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2880,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360696</v>
+        <v>360670</v>
       </c>
       <c r="R20" t="n">
-        <v>6540881</v>
+        <v>6540973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2916,11 +2921,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,53 +3069,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130433159</v>
+        <v>130433098</v>
       </c>
       <c r="B22" t="n">
-        <v>101146</v>
+        <v>58013</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>360652</v>
+        <v>360645</v>
       </c>
       <c r="R22" t="n">
-        <v>6540954</v>
+        <v>6540888</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3161,13 +3169,17 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3185,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433101</v>
+        <v>130433159</v>
       </c>
       <c r="B23" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3196,21 +3208,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360701</v>
+        <v>360652</v>
       </c>
       <c r="R23" t="n">
-        <v>6540855</v>
+        <v>6540954</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3268,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3283,7 +3295,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3301,7 +3313,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433105</v>
+        <v>130433101</v>
       </c>
       <c r="B24" t="n">
         <v>111114</v>
@@ -3344,10 +3356,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360726</v>
+        <v>360701</v>
       </c>
       <c r="R24" t="n">
-        <v>6540873</v>
+        <v>6540855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3384,7 +3396,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3417,61 +3429,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433098</v>
+        <v>130433105</v>
       </c>
       <c r="B25" t="n">
-        <v>58013</v>
+        <v>111114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360645</v>
+        <v>360726</v>
       </c>
       <c r="R25" t="n">
-        <v>6540888</v>
+        <v>6540873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3508,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3517,17 +3521,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433102</v>
+        <v>130433149</v>
       </c>
       <c r="B27" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360627</v>
+        <v>360769</v>
       </c>
       <c r="R27" t="n">
-        <v>6540799</v>
+        <v>6540905</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433149</v>
+        <v>130433102</v>
       </c>
       <c r="B28" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360769</v>
+        <v>360627</v>
       </c>
       <c r="R28" t="n">
-        <v>6540905</v>
+        <v>6540799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4609,10 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433103</v>
+        <v>130433160</v>
       </c>
       <c r="B35" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360640</v>
+        <v>360656</v>
       </c>
       <c r="R35" t="n">
-        <v>6540794</v>
+        <v>6540928</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,11 +4688,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4725,7 +4720,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433160</v>
+        <v>130433147</v>
       </c>
       <c r="B36" t="n">
         <v>101146</v>
@@ -4768,10 +4763,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360656</v>
+        <v>360645</v>
       </c>
       <c r="R36" t="n">
-        <v>6540928</v>
+        <v>6540790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4804,6 +4799,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433147</v>
+        <v>130433103</v>
       </c>
       <c r="B37" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360645</v>
+        <v>360640</v>
       </c>
       <c r="R37" t="n">
-        <v>6540790</v>
+        <v>6540794</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130433120</v>
+        <v>130433151</v>
       </c>
       <c r="B3" t="n">
-        <v>58226</v>
+        <v>101146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,50 +817,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>360722</v>
+        <v>360741</v>
       </c>
       <c r="R3" t="n">
-        <v>6540833</v>
+        <v>6540886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +898,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -929,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130433151</v>
+        <v>130433152</v>
       </c>
       <c r="B4" t="n">
         <v>101146</v>
@@ -972,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360741</v>
+        <v>360683</v>
       </c>
       <c r="R4" t="n">
-        <v>6540886</v>
+        <v>6540849</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130433152</v>
+        <v>130433143</v>
       </c>
       <c r="B5" t="n">
         <v>101146</v>
@@ -1088,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360683</v>
+        <v>360644</v>
       </c>
       <c r="R5" t="n">
-        <v>6540849</v>
+        <v>6540876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkbarrskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130433143</v>
+        <v>130433120</v>
       </c>
       <c r="B6" t="n">
-        <v>101146</v>
+        <v>58226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,42 +1165,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360644</v>
+        <v>360722</v>
       </c>
       <c r="R6" t="n">
-        <v>6540876</v>
+        <v>6540833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1254,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433115</v>
+        <v>130433116</v>
       </c>
       <c r="B8" t="n">
         <v>57851</v>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360725</v>
+        <v>360751</v>
       </c>
       <c r="R8" t="n">
-        <v>6540811</v>
+        <v>6540820</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433116</v>
+        <v>130433115</v>
       </c>
       <c r="B9" t="n">
         <v>57851</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360751</v>
+        <v>360725</v>
       </c>
       <c r="R9" t="n">
-        <v>6540820</v>
+        <v>6540811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R15" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R16" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433100</v>
+        <v>130433108</v>
       </c>
       <c r="B17" t="n">
         <v>111114</v>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360646</v>
+        <v>360696</v>
       </c>
       <c r="R17" t="n">
-        <v>6540820</v>
+        <v>6540881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,7 +2610,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433108</v>
+        <v>130433100</v>
       </c>
       <c r="B18" t="n">
         <v>111114</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360696</v>
+        <v>360646</v>
       </c>
       <c r="R18" t="n">
-        <v>6540881</v>
+        <v>6540820</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433159</v>
+        <v>130433105</v>
       </c>
       <c r="B23" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360652</v>
+        <v>360726</v>
       </c>
       <c r="R23" t="n">
-        <v>6540954</v>
+        <v>6540873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433105</v>
+        <v>130433159</v>
       </c>
       <c r="B25" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,21 +3440,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360726</v>
+        <v>360652</v>
       </c>
       <c r="R25" t="n">
-        <v>6540873</v>
+        <v>6540954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B26" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R26" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,11 +3644,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3666,7 +3661,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433149</v>
+        <v>130433155</v>
       </c>
       <c r="B27" t="n">
         <v>101146</v>
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360769</v>
+        <v>360610</v>
       </c>
       <c r="R27" t="n">
-        <v>6540905</v>
+        <v>6540895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,6 +3760,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433102</v>
+        <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360627</v>
+        <v>360769</v>
       </c>
       <c r="R28" t="n">
-        <v>6540799</v>
+        <v>6540905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4952,53 +4952,61 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B38" t="n">
-        <v>101146</v>
+        <v>57851</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R38" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5035,7 +5043,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5044,7 +5052,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5068,61 +5075,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>57851</v>
+        <v>101146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R39" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5159,7 +5158,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5168,6 +5167,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130433151</v>
+        <v>130433120</v>
       </c>
       <c r="B3" t="n">
-        <v>101146</v>
+        <v>58226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,42 +817,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>360741</v>
+        <v>360722</v>
       </c>
       <c r="R3" t="n">
-        <v>6540886</v>
+        <v>6540833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +906,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,7 +929,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130433152</v>
+        <v>130433151</v>
       </c>
       <c r="B4" t="n">
         <v>101146</v>
@@ -965,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360683</v>
+        <v>360741</v>
       </c>
       <c r="R4" t="n">
-        <v>6540849</v>
+        <v>6540886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkbarrskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1045,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130433143</v>
+        <v>130433152</v>
       </c>
       <c r="B5" t="n">
         <v>101146</v>
@@ -1081,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360644</v>
+        <v>360683</v>
       </c>
       <c r="R5" t="n">
-        <v>6540876</v>
+        <v>6540849</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130433120</v>
+        <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>58226</v>
+        <v>101146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,50 +1172,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360722</v>
+        <v>360644</v>
       </c>
       <c r="R6" t="n">
-        <v>6540833</v>
+        <v>6540876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,6 +1253,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433116</v>
+        <v>130433115</v>
       </c>
       <c r="B8" t="n">
         <v>57851</v>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360751</v>
+        <v>360725</v>
       </c>
       <c r="R8" t="n">
-        <v>6540820</v>
+        <v>6540811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433115</v>
+        <v>130433116</v>
       </c>
       <c r="B9" t="n">
         <v>57851</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360725</v>
+        <v>360751</v>
       </c>
       <c r="R9" t="n">
-        <v>6540811</v>
+        <v>6540820</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R10" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R11" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R15" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R16" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433108</v>
+        <v>130433144</v>
       </c>
       <c r="B17" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360696</v>
+        <v>360645</v>
       </c>
       <c r="R17" t="n">
-        <v>6540881</v>
+        <v>6540823</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433100</v>
+        <v>130433161</v>
       </c>
       <c r="B18" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360646</v>
+        <v>360670</v>
       </c>
       <c r="R18" t="n">
-        <v>6540820</v>
+        <v>6540973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,11 +2689,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,7 +2721,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433144</v>
+        <v>130433145</v>
       </c>
       <c r="B19" t="n">
         <v>101146</v>
@@ -2769,10 +2764,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360645</v>
+        <v>360628</v>
       </c>
       <c r="R19" t="n">
-        <v>6540823</v>
+        <v>6540817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2809,7 +2804,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433161</v>
+        <v>130433100</v>
       </c>
       <c r="B20" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,21 +2848,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360670</v>
+        <v>360646</v>
       </c>
       <c r="R20" t="n">
-        <v>6540973</v>
+        <v>6540820</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,6 +2916,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433145</v>
+        <v>130433108</v>
       </c>
       <c r="B21" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360628</v>
+        <v>360696</v>
       </c>
       <c r="R21" t="n">
-        <v>6540817</v>
+        <v>6540881</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433105</v>
+        <v>130433159</v>
       </c>
       <c r="B23" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360726</v>
+        <v>360652</v>
       </c>
       <c r="R23" t="n">
-        <v>6540873</v>
+        <v>6540954</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433159</v>
+        <v>130433105</v>
       </c>
       <c r="B25" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,21 +3440,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360652</v>
+        <v>360726</v>
       </c>
       <c r="R25" t="n">
-        <v>6540954</v>
+        <v>6540873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433102</v>
+        <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>111114</v>
+        <v>101146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360627</v>
+        <v>360610</v>
       </c>
       <c r="R26" t="n">
-        <v>6540799</v>
+        <v>6540895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,6 +3644,11 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3661,7 +3666,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433155</v>
+        <v>130433149</v>
       </c>
       <c r="B27" t="n">
         <v>101146</v>
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360610</v>
+        <v>360769</v>
       </c>
       <c r="R27" t="n">
-        <v>6540895</v>
+        <v>6540905</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,11 +3765,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433149</v>
+        <v>130433102</v>
       </c>
       <c r="B28" t="n">
-        <v>101146</v>
+        <v>111114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360769</v>
+        <v>360627</v>
       </c>
       <c r="R28" t="n">
-        <v>6540905</v>
+        <v>6540799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4952,61 +4952,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B38" t="n">
-        <v>57851</v>
+        <v>101146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R38" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5043,7 +5035,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5052,6 +5044,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5075,53 +5068,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B39" t="n">
-        <v>101146</v>
+        <v>57851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R39" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5167,7 +5168,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130433120</v>
       </c>
       <c r="B3" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,42 +1277,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433109</v>
+        <v>130433115</v>
       </c>
       <c r="B7" t="n">
-        <v>111114</v>
+        <v>57859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360689</v>
+        <v>360725</v>
       </c>
       <c r="R7" t="n">
-        <v>6540864</v>
+        <v>6540811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,13 +1369,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1393,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433115</v>
+        <v>130433116</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360725</v>
+        <v>360751</v>
       </c>
       <c r="R8" t="n">
-        <v>6540811</v>
+        <v>6540820</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1495,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,12 +1524,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1528,42 +1547,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433116</v>
+        <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>111127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1571,10 +1590,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360751</v>
+        <v>360689</v>
       </c>
       <c r="R9" t="n">
-        <v>6540820</v>
+        <v>6540864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1630,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,32 +1639,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
         <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433118</v>
+        <v>130433110</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>111127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360679</v>
+        <v>360682</v>
       </c>
       <c r="R12" t="n">
-        <v>6540844</v>
+        <v>6540850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,32 +1987,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2030,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433110</v>
+        <v>130433111</v>
       </c>
       <c r="B13" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360682</v>
+        <v>360659</v>
       </c>
       <c r="R13" t="n">
-        <v>6540850</v>
+        <v>6540849</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,42 +2127,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433111</v>
+        <v>130433118</v>
       </c>
       <c r="B14" t="n">
-        <v>111114</v>
+        <v>57859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2189,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360659</v>
+        <v>360679</v>
       </c>
       <c r="R14" t="n">
-        <v>6540849</v>
+        <v>6540844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,13 +2219,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
         <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>130433144</v>
       </c>
       <c r="B17" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>130433161</v>
       </c>
       <c r="B18" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>130433145</v>
       </c>
       <c r="B19" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433100</v>
+        <v>130433108</v>
       </c>
       <c r="B20" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360646</v>
+        <v>360696</v>
       </c>
       <c r="R20" t="n">
-        <v>6540820</v>
+        <v>6540881</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433108</v>
+        <v>130433100</v>
       </c>
       <c r="B21" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360696</v>
+        <v>360646</v>
       </c>
       <c r="R21" t="n">
-        <v>6540881</v>
+        <v>6540820</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3069,61 +3069,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130433098</v>
+        <v>130433159</v>
       </c>
       <c r="B22" t="n">
-        <v>58013</v>
+        <v>101159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>360645</v>
+        <v>360652</v>
       </c>
       <c r="R22" t="n">
-        <v>6540888</v>
+        <v>6540954</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3160,7 +3152,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3169,17 +3161,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3197,10 +3185,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433159</v>
+        <v>130433105</v>
       </c>
       <c r="B23" t="n">
-        <v>101146</v>
+        <v>111127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,21 +3196,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3240,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360652</v>
+        <v>360726</v>
       </c>
       <c r="R23" t="n">
-        <v>6540954</v>
+        <v>6540873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3268,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3283,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3316,7 +3304,7 @@
         <v>130433101</v>
       </c>
       <c r="B24" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,53 +3417,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433105</v>
+        <v>130433098</v>
       </c>
       <c r="B25" t="n">
-        <v>111114</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360726</v>
+        <v>360645</v>
       </c>
       <c r="R25" t="n">
-        <v>6540873</v>
+        <v>6540888</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3508,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3521,13 +3517,17 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>130433149</v>
       </c>
       <c r="B27" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>130433102</v>
       </c>
       <c r="B28" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>130433160</v>
       </c>
       <c r="B35" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>130433147</v>
       </c>
       <c r="B36" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>130433103</v>
       </c>
       <c r="B37" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4952,53 +4952,61 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B38" t="n">
-        <v>101146</v>
+        <v>57859</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R38" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5035,7 +5043,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5044,7 +5052,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5068,61 +5075,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>57851</v>
+        <v>101159</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R39" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5159,7 +5158,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5168,6 +5167,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130433120</v>
       </c>
       <c r="B3" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130433115</v>
       </c>
       <c r="B7" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>130433116</v>
       </c>
       <c r="B8" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433110</v>
+        <v>130433118</v>
       </c>
       <c r="B12" t="n">
-        <v>111127</v>
+        <v>57860</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360682</v>
+        <v>360679</v>
       </c>
       <c r="R12" t="n">
-        <v>6540850</v>
+        <v>6540844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,13 +1987,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,10 +2030,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433111</v>
+        <v>130433110</v>
       </c>
       <c r="B13" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,10 +2073,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360659</v>
+        <v>360682</v>
       </c>
       <c r="R13" t="n">
-        <v>6540849</v>
+        <v>6540850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2127,42 +2146,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433118</v>
+        <v>130433111</v>
       </c>
       <c r="B14" t="n">
-        <v>57859</v>
+        <v>111128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360679</v>
+        <v>360659</v>
       </c>
       <c r="R14" t="n">
-        <v>6540844</v>
+        <v>6540849</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2229,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,32 +2238,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>101159</v>
+        <v>111128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R15" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>111127</v>
+        <v>101160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R16" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433144</v>
+        <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>101159</v>
+        <v>111128</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360645</v>
+        <v>360646</v>
       </c>
       <c r="R17" t="n">
-        <v>6540823</v>
+        <v>6540820</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433161</v>
+        <v>130433108</v>
       </c>
       <c r="B18" t="n">
-        <v>101159</v>
+        <v>111128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360670</v>
+        <v>360696</v>
       </c>
       <c r="R18" t="n">
-        <v>6540973</v>
+        <v>6540881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,6 +2689,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,10 +2726,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433145</v>
+        <v>130433144</v>
       </c>
       <c r="B19" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360628</v>
+        <v>360645</v>
       </c>
       <c r="R19" t="n">
-        <v>6540817</v>
+        <v>6540823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2804,7 +2809,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433108</v>
+        <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>111127</v>
+        <v>101160</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2880,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360696</v>
+        <v>360670</v>
       </c>
       <c r="R20" t="n">
-        <v>6540881</v>
+        <v>6540973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2916,11 +2921,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433100</v>
+        <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>111127</v>
+        <v>101160</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360646</v>
+        <v>360628</v>
       </c>
       <c r="R21" t="n">
-        <v>6540820</v>
+        <v>6540817</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3069,53 +3069,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130433159</v>
+        <v>130433098</v>
       </c>
       <c r="B22" t="n">
-        <v>101159</v>
+        <v>58022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>360652</v>
+        <v>360645</v>
       </c>
       <c r="R22" t="n">
-        <v>6540954</v>
+        <v>6540888</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3161,13 +3169,17 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3185,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433105</v>
+        <v>130433101</v>
       </c>
       <c r="B23" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3228,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360726</v>
+        <v>360701</v>
       </c>
       <c r="R23" t="n">
-        <v>6540873</v>
+        <v>6540855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3268,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,10 +3313,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433101</v>
+        <v>130433105</v>
       </c>
       <c r="B24" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,10 +3356,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360701</v>
+        <v>360726</v>
       </c>
       <c r="R24" t="n">
-        <v>6540855</v>
+        <v>6540873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3384,7 +3396,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3417,61 +3429,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433098</v>
+        <v>130433159</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>101160</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360645</v>
+        <v>360652</v>
       </c>
       <c r="R25" t="n">
-        <v>6540888</v>
+        <v>6540954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3508,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3517,17 +3521,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B26" t="n">
-        <v>101159</v>
+        <v>111128</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R26" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,11 +3644,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3666,10 +3661,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433149</v>
+        <v>130433155</v>
       </c>
       <c r="B27" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360769</v>
+        <v>360610</v>
       </c>
       <c r="R27" t="n">
-        <v>6540905</v>
+        <v>6540895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,6 +3760,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433102</v>
+        <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>111127</v>
+        <v>101160</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360627</v>
+        <v>360769</v>
       </c>
       <c r="R28" t="n">
-        <v>6540799</v>
+        <v>6540905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433160</v>
+        <v>130433103</v>
       </c>
       <c r="B35" t="n">
-        <v>101159</v>
+        <v>111128</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360656</v>
+        <v>360640</v>
       </c>
       <c r="R35" t="n">
-        <v>6540928</v>
+        <v>6540794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,6 +4688,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4720,10 +4725,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433147</v>
+        <v>130433160</v>
       </c>
       <c r="B36" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4763,10 +4768,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360645</v>
+        <v>360656</v>
       </c>
       <c r="R36" t="n">
-        <v>6540790</v>
+        <v>6540928</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4799,11 +4804,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433103</v>
+        <v>130433147</v>
       </c>
       <c r="B37" t="n">
-        <v>111127</v>
+        <v>101160</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360640</v>
+        <v>360645</v>
       </c>
       <c r="R37" t="n">
-        <v>6540794</v>
+        <v>6540790</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,61 +4952,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B38" t="n">
-        <v>57859</v>
+        <v>101160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R38" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5043,7 +5035,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5052,6 +5044,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5075,53 +5068,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B39" t="n">
-        <v>101159</v>
+        <v>57860</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R39" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5167,7 +5168,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130433120</v>
       </c>
       <c r="B3" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130433115</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>130433116</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433118</v>
+        <v>130433110</v>
       </c>
       <c r="B12" t="n">
-        <v>57860</v>
+        <v>111131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360679</v>
+        <v>360682</v>
       </c>
       <c r="R12" t="n">
-        <v>6540844</v>
+        <v>6540850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,32 +1987,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2030,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433110</v>
+        <v>130433111</v>
       </c>
       <c r="B13" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360682</v>
+        <v>360659</v>
       </c>
       <c r="R13" t="n">
-        <v>6540850</v>
+        <v>6540849</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,42 +2127,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433111</v>
+        <v>130433118</v>
       </c>
       <c r="B14" t="n">
-        <v>111128</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2189,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360659</v>
+        <v>360679</v>
       </c>
       <c r="R14" t="n">
-        <v>6540849</v>
+        <v>6540844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,13 +2219,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>111128</v>
+        <v>101163</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R15" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>101160</v>
+        <v>111131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R16" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433100</v>
+        <v>130433144</v>
       </c>
       <c r="B17" t="n">
-        <v>111128</v>
+        <v>101163</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360646</v>
+        <v>360645</v>
       </c>
       <c r="R17" t="n">
-        <v>6540820</v>
+        <v>6540823</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433108</v>
+        <v>130433161</v>
       </c>
       <c r="B18" t="n">
-        <v>111128</v>
+        <v>101163</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360696</v>
+        <v>360670</v>
       </c>
       <c r="R18" t="n">
-        <v>6540881</v>
+        <v>6540973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,11 +2689,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433144</v>
+        <v>130433145</v>
       </c>
       <c r="B19" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,10 +2764,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360645</v>
+        <v>360628</v>
       </c>
       <c r="R19" t="n">
-        <v>6540823</v>
+        <v>6540817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2809,7 +2804,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433161</v>
+        <v>130433108</v>
       </c>
       <c r="B20" t="n">
-        <v>101160</v>
+        <v>111131</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,21 +2848,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360670</v>
+        <v>360696</v>
       </c>
       <c r="R20" t="n">
-        <v>6540973</v>
+        <v>6540881</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,6 +2916,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433145</v>
+        <v>130433100</v>
       </c>
       <c r="B21" t="n">
-        <v>101160</v>
+        <v>111131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360628</v>
+        <v>360646</v>
       </c>
       <c r="R21" t="n">
-        <v>6540817</v>
+        <v>6540820</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3072,7 +3072,7 @@
         <v>130433098</v>
       </c>
       <c r="B22" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433101</v>
+        <v>130433159</v>
       </c>
       <c r="B23" t="n">
-        <v>111128</v>
+        <v>101163</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360701</v>
+        <v>360652</v>
       </c>
       <c r="R23" t="n">
-        <v>6540855</v>
+        <v>6540954</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
         <v>130433105</v>
       </c>
       <c r="B24" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433159</v>
+        <v>130433101</v>
       </c>
       <c r="B25" t="n">
-        <v>101160</v>
+        <v>111131</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,21 +3440,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360652</v>
+        <v>360701</v>
       </c>
       <c r="R25" t="n">
-        <v>6540954</v>
+        <v>6540855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433102</v>
+        <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>111128</v>
+        <v>101163</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360627</v>
+        <v>360610</v>
       </c>
       <c r="R26" t="n">
-        <v>6540799</v>
+        <v>6540895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,6 +3644,11 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3661,10 +3666,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433155</v>
+        <v>130433149</v>
       </c>
       <c r="B27" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360610</v>
+        <v>360769</v>
       </c>
       <c r="R27" t="n">
-        <v>6540895</v>
+        <v>6540905</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,11 +3765,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433149</v>
+        <v>130433102</v>
       </c>
       <c r="B28" t="n">
-        <v>101160</v>
+        <v>111131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360769</v>
+        <v>360627</v>
       </c>
       <c r="R28" t="n">
-        <v>6540905</v>
+        <v>6540799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433103</v>
+        <v>130433160</v>
       </c>
       <c r="B35" t="n">
-        <v>111128</v>
+        <v>101163</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360640</v>
+        <v>360656</v>
       </c>
       <c r="R35" t="n">
-        <v>6540794</v>
+        <v>6540928</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,11 +4688,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4725,10 +4720,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433160</v>
+        <v>130433147</v>
       </c>
       <c r="B36" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,10 +4763,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360656</v>
+        <v>360645</v>
       </c>
       <c r="R36" t="n">
-        <v>6540928</v>
+        <v>6540790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4804,6 +4799,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433147</v>
+        <v>130433103</v>
       </c>
       <c r="B37" t="n">
-        <v>101160</v>
+        <v>111131</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360645</v>
+        <v>360640</v>
       </c>
       <c r="R37" t="n">
-        <v>6540790</v>
+        <v>6540794</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,53 +4952,61 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B38" t="n">
-        <v>101160</v>
+        <v>57861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R38" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5035,7 +5043,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5044,7 +5052,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5068,61 +5075,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>57860</v>
+        <v>101163</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R39" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5159,7 +5158,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5168,6 +5167,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -1277,42 +1277,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433115</v>
+        <v>130433109</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>111131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360725</v>
+        <v>360689</v>
       </c>
       <c r="R7" t="n">
-        <v>6540811</v>
+        <v>6540864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,32 +1369,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433116</v>
+        <v>130433115</v>
       </c>
       <c r="B8" t="n">
         <v>57861</v>
@@ -1455,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360751</v>
+        <v>360725</v>
       </c>
       <c r="R8" t="n">
-        <v>6540820</v>
+        <v>6540811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,12 +1505,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1547,42 +1528,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433109</v>
+        <v>130433116</v>
       </c>
       <c r="B9" t="n">
-        <v>111131</v>
+        <v>57861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1590,10 +1571,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360689</v>
+        <v>360751</v>
       </c>
       <c r="R9" t="n">
-        <v>6540864</v>
+        <v>6540820</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,7 +1611,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,13 +1620,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433110</v>
+        <v>130433118</v>
       </c>
       <c r="B12" t="n">
-        <v>111131</v>
+        <v>57861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360682</v>
+        <v>360679</v>
       </c>
       <c r="R12" t="n">
-        <v>6540850</v>
+        <v>6540844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,13 +1987,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,7 +2030,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433111</v>
+        <v>130433110</v>
       </c>
       <c r="B13" t="n">
         <v>111131</v>
@@ -2054,10 +2073,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360659</v>
+        <v>360682</v>
       </c>
       <c r="R13" t="n">
-        <v>6540849</v>
+        <v>6540850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2127,42 +2146,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433118</v>
+        <v>130433111</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>111131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360679</v>
+        <v>360659</v>
       </c>
       <c r="R14" t="n">
-        <v>6540844</v>
+        <v>6540849</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2229,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,32 +2238,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433108</v>
+        <v>130433100</v>
       </c>
       <c r="B20" t="n">
         <v>111131</v>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360696</v>
+        <v>360646</v>
       </c>
       <c r="R20" t="n">
-        <v>6540881</v>
+        <v>6540820</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,7 +2953,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433100</v>
+        <v>130433108</v>
       </c>
       <c r="B21" t="n">
         <v>111131</v>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360646</v>
+        <v>360696</v>
       </c>
       <c r="R21" t="n">
-        <v>6540820</v>
+        <v>6540881</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3313,7 +3313,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433105</v>
+        <v>130433101</v>
       </c>
       <c r="B24" t="n">
         <v>111131</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360726</v>
+        <v>360701</v>
       </c>
       <c r="R24" t="n">
-        <v>6540873</v>
+        <v>6540855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3429,7 +3429,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433101</v>
+        <v>130433105</v>
       </c>
       <c r="B25" t="n">
         <v>111131</v>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360701</v>
+        <v>360726</v>
       </c>
       <c r="R25" t="n">
-        <v>6540855</v>
+        <v>6540873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4952,61 +4952,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
+        <v>101163</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R38" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5043,7 +5035,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5052,6 +5044,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5075,53 +5068,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B39" t="n">
-        <v>101163</v>
+        <v>57861</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R39" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5167,7 +5168,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -1277,42 +1277,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433109</v>
+        <v>130433116</v>
       </c>
       <c r="B7" t="n">
-        <v>111131</v>
+        <v>57861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360689</v>
+        <v>360751</v>
       </c>
       <c r="R7" t="n">
-        <v>6540864</v>
+        <v>6540820</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,13 +1369,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1528,42 +1547,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433116</v>
+        <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>111131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1571,10 +1590,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360751</v>
+        <v>360689</v>
       </c>
       <c r="R9" t="n">
-        <v>6540820</v>
+        <v>6540864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1630,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,32 +1639,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B10" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R10" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B11" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R11" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R15" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R16" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433144</v>
+        <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360645</v>
+        <v>360646</v>
       </c>
       <c r="R17" t="n">
-        <v>6540823</v>
+        <v>6540820</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433161</v>
+        <v>130433108</v>
       </c>
       <c r="B18" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360670</v>
+        <v>360696</v>
       </c>
       <c r="R18" t="n">
-        <v>6540973</v>
+        <v>6540881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,6 +2689,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,7 +2726,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433145</v>
+        <v>130433144</v>
       </c>
       <c r="B19" t="n">
         <v>101163</v>
@@ -2764,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360628</v>
+        <v>360645</v>
       </c>
       <c r="R19" t="n">
-        <v>6540817</v>
+        <v>6540823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2804,7 +2809,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433100</v>
+        <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2880,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360646</v>
+        <v>360670</v>
       </c>
       <c r="R20" t="n">
-        <v>6540820</v>
+        <v>6540973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2916,11 +2921,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433108</v>
+        <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360696</v>
+        <v>360628</v>
       </c>
       <c r="R21" t="n">
-        <v>6540881</v>
+        <v>6540817</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433159</v>
+        <v>130433101</v>
       </c>
       <c r="B23" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360652</v>
+        <v>360701</v>
       </c>
       <c r="R23" t="n">
-        <v>6540954</v>
+        <v>6540855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433101</v>
+        <v>130433105</v>
       </c>
       <c r="B24" t="n">
         <v>111131</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360701</v>
+        <v>360726</v>
       </c>
       <c r="R24" t="n">
-        <v>6540855</v>
+        <v>6540873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3429,10 +3429,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433105</v>
+        <v>130433159</v>
       </c>
       <c r="B25" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,21 +3440,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360726</v>
+        <v>360652</v>
       </c>
       <c r="R25" t="n">
-        <v>6540873</v>
+        <v>6540954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B26" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R26" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,11 +3644,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3666,7 +3661,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433149</v>
+        <v>130433155</v>
       </c>
       <c r="B27" t="n">
         <v>101163</v>
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360769</v>
+        <v>360610</v>
       </c>
       <c r="R27" t="n">
-        <v>6540905</v>
+        <v>6540895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,6 +3760,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433102</v>
+        <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360627</v>
+        <v>360769</v>
       </c>
       <c r="R28" t="n">
-        <v>6540799</v>
+        <v>6540905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4609,7 +4609,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433160</v>
+        <v>130433147</v>
       </c>
       <c r="B35" t="n">
         <v>101163</v>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360656</v>
+        <v>360645</v>
       </c>
       <c r="R35" t="n">
-        <v>6540928</v>
+        <v>6540790</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,6 +4688,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4720,10 +4725,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433147</v>
+        <v>130433103</v>
       </c>
       <c r="B36" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4731,21 +4736,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4763,10 +4768,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360645</v>
+        <v>360640</v>
       </c>
       <c r="R36" t="n">
-        <v>6540790</v>
+        <v>6540794</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4803,7 +4808,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,10 +4841,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433103</v>
+        <v>130433160</v>
       </c>
       <c r="B37" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4852,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4884,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360640</v>
+        <v>360656</v>
       </c>
       <c r="R37" t="n">
-        <v>6540794</v>
+        <v>6540928</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4915,11 +4920,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,53 +4952,61 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B38" t="n">
-        <v>101163</v>
+        <v>57861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R38" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5035,7 +5043,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5044,7 +5052,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5068,61 +5075,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>57861</v>
+        <v>101163</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R39" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5159,7 +5158,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5168,6 +5167,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -1277,42 +1277,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433116</v>
+        <v>130433109</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>111131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360751</v>
+        <v>360689</v>
       </c>
       <c r="R7" t="n">
-        <v>6540820</v>
+        <v>6540864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,32 +1369,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1547,42 +1528,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433109</v>
+        <v>130433116</v>
       </c>
       <c r="B9" t="n">
-        <v>111131</v>
+        <v>57861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1590,10 +1571,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360689</v>
+        <v>360751</v>
       </c>
       <c r="R9" t="n">
-        <v>6540864</v>
+        <v>6540820</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,7 +1611,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,13 +1620,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433147</v>
+        <v>130433160</v>
       </c>
       <c r="B35" t="n">
         <v>101163</v>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360645</v>
+        <v>360656</v>
       </c>
       <c r="R35" t="n">
-        <v>6540790</v>
+        <v>6540928</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,11 +4688,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4725,10 +4720,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433103</v>
+        <v>130433147</v>
       </c>
       <c r="B36" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,21 +4731,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4768,10 +4763,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360640</v>
+        <v>360645</v>
       </c>
       <c r="R36" t="n">
-        <v>6540794</v>
+        <v>6540790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4808,7 +4803,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4841,10 +4836,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433160</v>
+        <v>130433103</v>
       </c>
       <c r="B37" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,21 +4847,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4884,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360656</v>
+        <v>360640</v>
       </c>
       <c r="R37" t="n">
-        <v>6540928</v>
+        <v>6540794</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4920,6 +4915,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130433120</v>
+        <v>130433151</v>
       </c>
       <c r="B3" t="n">
-        <v>58236</v>
+        <v>101163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,50 +817,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>360722</v>
+        <v>360741</v>
       </c>
       <c r="R3" t="n">
-        <v>6540833</v>
+        <v>6540886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +898,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -929,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130433151</v>
+        <v>130433152</v>
       </c>
       <c r="B4" t="n">
         <v>101163</v>
@@ -972,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360741</v>
+        <v>360683</v>
       </c>
       <c r="R4" t="n">
-        <v>6540886</v>
+        <v>6540849</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130433152</v>
+        <v>130433143</v>
       </c>
       <c r="B5" t="n">
         <v>101163</v>
@@ -1088,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360683</v>
+        <v>360644</v>
       </c>
       <c r="R5" t="n">
-        <v>6540849</v>
+        <v>6540876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkbarrskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130433143</v>
+        <v>130433120</v>
       </c>
       <c r="B6" t="n">
-        <v>101163</v>
+        <v>58236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,42 +1165,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360644</v>
+        <v>360722</v>
       </c>
       <c r="R6" t="n">
-        <v>6540876</v>
+        <v>6540833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1254,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1277,42 +1277,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433109</v>
+        <v>130433116</v>
       </c>
       <c r="B7" t="n">
-        <v>111131</v>
+        <v>57861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360689</v>
+        <v>360751</v>
       </c>
       <c r="R7" t="n">
-        <v>6540864</v>
+        <v>6540820</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,13 +1369,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1528,42 +1547,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130433116</v>
+        <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>111131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1571,10 +1590,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>360751</v>
+        <v>360689</v>
       </c>
       <c r="R9" t="n">
-        <v>6540820</v>
+        <v>6540864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1630,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,32 +1639,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R10" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R11" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R15" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R16" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433100</v>
+        <v>130433144</v>
       </c>
       <c r="B17" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360646</v>
+        <v>360645</v>
       </c>
       <c r="R17" t="n">
-        <v>6540820</v>
+        <v>6540823</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433108</v>
+        <v>130433161</v>
       </c>
       <c r="B18" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360696</v>
+        <v>360670</v>
       </c>
       <c r="R18" t="n">
-        <v>6540881</v>
+        <v>6540973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,11 +2689,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,7 +2721,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433144</v>
+        <v>130433145</v>
       </c>
       <c r="B19" t="n">
         <v>101163</v>
@@ -2769,10 +2764,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360645</v>
+        <v>360628</v>
       </c>
       <c r="R19" t="n">
-        <v>6540823</v>
+        <v>6540817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2809,7 +2804,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433161</v>
+        <v>130433108</v>
       </c>
       <c r="B20" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,21 +2848,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360670</v>
+        <v>360696</v>
       </c>
       <c r="R20" t="n">
-        <v>6540973</v>
+        <v>6540881</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,6 +2916,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433145</v>
+        <v>130433100</v>
       </c>
       <c r="B21" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360628</v>
+        <v>360646</v>
       </c>
       <c r="R21" t="n">
-        <v>6540817</v>
+        <v>6540820</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3069,61 +3069,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130433098</v>
+        <v>130433105</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>111131</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>360645</v>
+        <v>360726</v>
       </c>
       <c r="R22" t="n">
-        <v>6540888</v>
+        <v>6540873</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3160,7 +3152,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3169,17 +3161,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3313,53 +3301,61 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433105</v>
+        <v>130433098</v>
       </c>
       <c r="B24" t="n">
-        <v>111131</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360726</v>
+        <v>360645</v>
       </c>
       <c r="R24" t="n">
-        <v>6540873</v>
+        <v>6540888</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3396,7 +3392,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3405,13 +3401,17 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433102</v>
+        <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360627</v>
+        <v>360610</v>
       </c>
       <c r="R26" t="n">
-        <v>6540799</v>
+        <v>6540895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,6 +3644,11 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3661,7 +3666,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433155</v>
+        <v>130433149</v>
       </c>
       <c r="B27" t="n">
         <v>101163</v>
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360610</v>
+        <v>360769</v>
       </c>
       <c r="R27" t="n">
-        <v>6540895</v>
+        <v>6540905</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,11 +3765,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433149</v>
+        <v>130433102</v>
       </c>
       <c r="B28" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360769</v>
+        <v>360627</v>
       </c>
       <c r="R28" t="n">
-        <v>6540905</v>
+        <v>6540799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130433151</v>
+        <v>130433120</v>
       </c>
       <c r="B3" t="n">
-        <v>101163</v>
+        <v>58236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,42 +817,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>360741</v>
+        <v>360722</v>
       </c>
       <c r="R3" t="n">
-        <v>6540886</v>
+        <v>6540833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +906,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,7 +929,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130433152</v>
+        <v>130433151</v>
       </c>
       <c r="B4" t="n">
         <v>101163</v>
@@ -965,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360683</v>
+        <v>360741</v>
       </c>
       <c r="R4" t="n">
-        <v>6540849</v>
+        <v>6540886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkbarrskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1045,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130433143</v>
+        <v>130433152</v>
       </c>
       <c r="B5" t="n">
         <v>101163</v>
@@ -1081,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360644</v>
+        <v>360683</v>
       </c>
       <c r="R5" t="n">
-        <v>6540876</v>
+        <v>6540849</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130433120</v>
+        <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>58236</v>
+        <v>101163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,50 +1172,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360722</v>
+        <v>360644</v>
       </c>
       <c r="R6" t="n">
-        <v>6540833</v>
+        <v>6540876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i bitvis flerskiktad äldre granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,6 +1253,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130433116</v>
+        <v>130433115</v>
       </c>
       <c r="B7" t="n">
         <v>57861</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360751</v>
+        <v>360725</v>
       </c>
       <c r="R7" t="n">
-        <v>6540820</v>
+        <v>6540811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
+          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130433115</v>
+        <v>130433116</v>
       </c>
       <c r="B8" t="n">
         <v>57861</v>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360725</v>
+        <v>360751</v>
       </c>
       <c r="R8" t="n">
-        <v>6540811</v>
+        <v>6540820</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en stående grov död gran.</t>
+          <t>Rejäla äldre hackspår i en grov delvis nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B10" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R10" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B11" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R11" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433118</v>
+        <v>130433111</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>111131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360679</v>
+        <v>360659</v>
       </c>
       <c r="R12" t="n">
-        <v>6540844</v>
+        <v>6540849</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,32 +1987,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2030,42 +2011,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433110</v>
+        <v>130433118</v>
       </c>
       <c r="B13" t="n">
-        <v>111131</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2073,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360682</v>
+        <v>360679</v>
       </c>
       <c r="R13" t="n">
-        <v>6540850</v>
+        <v>6540844</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2113,7 +2094,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2122,13 +2103,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433111</v>
+        <v>130433110</v>
       </c>
       <c r="B14" t="n">
         <v>111131</v>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360659</v>
+        <v>360682</v>
       </c>
       <c r="R14" t="n">
-        <v>6540849</v>
+        <v>6540850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R15" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R16" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2837,7 +2837,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433108</v>
+        <v>130433100</v>
       </c>
       <c r="B20" t="n">
         <v>111131</v>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360696</v>
+        <v>360646</v>
       </c>
       <c r="R20" t="n">
-        <v>6540881</v>
+        <v>6540820</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,7 +2953,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433100</v>
+        <v>130433108</v>
       </c>
       <c r="B21" t="n">
         <v>111131</v>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360646</v>
+        <v>360696</v>
       </c>
       <c r="R21" t="n">
-        <v>6540820</v>
+        <v>6540881</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3069,10 +3069,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130433105</v>
+        <v>130433159</v>
       </c>
       <c r="B22" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,21 +3080,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>360726</v>
+        <v>360652</v>
       </c>
       <c r="R22" t="n">
-        <v>6540873</v>
+        <v>6540954</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3185,53 +3185,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433101</v>
+        <v>130433098</v>
       </c>
       <c r="B23" t="n">
-        <v>111131</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360701</v>
+        <v>360645</v>
       </c>
       <c r="R23" t="n">
-        <v>6540855</v>
+        <v>6540888</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3268,7 +3276,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3277,13 +3285,17 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3301,61 +3313,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130433098</v>
+        <v>130433101</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>111131</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>360645</v>
+        <v>360701</v>
       </c>
       <c r="R24" t="n">
-        <v>6540888</v>
+        <v>6540855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3392,7 +3396,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3401,17 +3405,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433159</v>
+        <v>130433105</v>
       </c>
       <c r="B25" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,21 +3440,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360652</v>
+        <v>360726</v>
       </c>
       <c r="R25" t="n">
-        <v>6540954</v>
+        <v>6540873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B26" t="n">
-        <v>101163</v>
+        <v>111131</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R26" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,11 +3644,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3666,7 +3661,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433149</v>
+        <v>130433155</v>
       </c>
       <c r="B27" t="n">
         <v>101163</v>
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360769</v>
+        <v>360610</v>
       </c>
       <c r="R27" t="n">
-        <v>6540905</v>
+        <v>6540895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,6 +3760,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433102</v>
+        <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>111131</v>
+        <v>101163</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360627</v>
+        <v>360769</v>
       </c>
       <c r="R28" t="n">
-        <v>6540799</v>
+        <v>6540905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4952,61 +4952,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
+        <v>101163</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R38" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5043,7 +5035,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5052,6 +5044,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5075,53 +5068,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B39" t="n">
-        <v>101163</v>
+        <v>57861</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R39" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5167,7 +5168,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130433113</v>
+        <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>111131</v>
+        <v>101177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>360606</v>
+        <v>360610</v>
       </c>
       <c r="R10" t="n">
-        <v>6540895</v>
+        <v>6540813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130433146</v>
+        <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>101163</v>
+        <v>111145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>360610</v>
+        <v>360606</v>
       </c>
       <c r="R11" t="n">
-        <v>6540813</v>
+        <v>6540895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Enstaka vintergröna blad i äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433111</v>
+        <v>130433118</v>
       </c>
       <c r="B12" t="n">
-        <v>111131</v>
+        <v>57861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360659</v>
+        <v>360679</v>
       </c>
       <c r="R12" t="n">
-        <v>6540849</v>
+        <v>6540844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,13 +1987,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,42 +2030,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433118</v>
+        <v>130433110</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>111145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2054,10 +2073,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360679</v>
+        <v>360682</v>
       </c>
       <c r="R13" t="n">
-        <v>6540844</v>
+        <v>6540850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2094,7 +2113,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,32 +2122,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433110</v>
+        <v>130433111</v>
       </c>
       <c r="B14" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360682</v>
+        <v>360659</v>
       </c>
       <c r="R14" t="n">
-        <v>6540850</v>
+        <v>6540849</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
         <v>130433106</v>
       </c>
       <c r="B15" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>130433157</v>
       </c>
       <c r="B16" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433144</v>
+        <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>101163</v>
+        <v>111145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360645</v>
+        <v>360646</v>
       </c>
       <c r="R17" t="n">
-        <v>6540823</v>
+        <v>6540820</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433161</v>
+        <v>130433144</v>
       </c>
       <c r="B18" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360670</v>
+        <v>360645</v>
       </c>
       <c r="R18" t="n">
-        <v>6540973</v>
+        <v>6540823</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,6 +2689,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,10 +2726,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433145</v>
+        <v>130433161</v>
       </c>
       <c r="B19" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360628</v>
+        <v>360670</v>
       </c>
       <c r="R19" t="n">
-        <v>6540817</v>
+        <v>6540973</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2800,11 +2805,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433100</v>
+        <v>130433108</v>
       </c>
       <c r="B20" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360646</v>
+        <v>360696</v>
       </c>
       <c r="R20" t="n">
-        <v>6540820</v>
+        <v>6540881</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130433108</v>
+        <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>111131</v>
+        <v>101177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>360696</v>
+        <v>360628</v>
       </c>
       <c r="R21" t="n">
-        <v>6540881</v>
+        <v>6540817</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3069,53 +3069,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130433159</v>
+        <v>130433098</v>
       </c>
       <c r="B22" t="n">
-        <v>101163</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>360652</v>
+        <v>360645</v>
       </c>
       <c r="R22" t="n">
-        <v>6540954</v>
+        <v>6540888</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3161,13 +3169,17 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3185,61 +3197,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433098</v>
+        <v>130433159</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>101177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360645</v>
+        <v>360652</v>
       </c>
       <c r="R23" t="n">
-        <v>6540888</v>
+        <v>6540954</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ i äldre bitvis flerskiktad granskog med inslag av björkhögstubbar. Möjligen hördes någon mer talltita i bakgrunden kring fyndplatsen.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3285,17 +3289,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre grandominerad skog med inslag av asp, björk, sälg, al och hassel.</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
         <v>130433101</v>
       </c>
       <c r="B24" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>130433105</v>
       </c>
       <c r="B25" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433102</v>
+        <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>111131</v>
+        <v>101177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360627</v>
+        <v>360610</v>
       </c>
       <c r="R26" t="n">
-        <v>6540799</v>
+        <v>6540895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,6 +3644,11 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3661,10 +3666,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B27" t="n">
-        <v>101163</v>
+        <v>111145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,21 +3677,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R27" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,11 +3765,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3785,7 +3785,7 @@
         <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433160</v>
+        <v>130433103</v>
       </c>
       <c r="B35" t="n">
-        <v>101163</v>
+        <v>111145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360656</v>
+        <v>360640</v>
       </c>
       <c r="R35" t="n">
-        <v>6540928</v>
+        <v>6540794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,6 +4688,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4720,10 +4725,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433147</v>
+        <v>130433160</v>
       </c>
       <c r="B36" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4763,10 +4768,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360645</v>
+        <v>360656</v>
       </c>
       <c r="R36" t="n">
-        <v>6540790</v>
+        <v>6540928</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4799,11 +4804,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433103</v>
+        <v>130433147</v>
       </c>
       <c r="B37" t="n">
-        <v>111131</v>
+        <v>101177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360640</v>
+        <v>360645</v>
       </c>
       <c r="R37" t="n">
-        <v>6540794</v>
+        <v>6540790</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,53 +4952,61 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B38" t="n">
-        <v>101163</v>
+        <v>57861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R38" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5035,7 +5043,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5044,7 +5052,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5068,61 +5075,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>57861</v>
+        <v>101177</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R39" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5159,7 +5158,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5168,6 +5167,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>130433151</v>
       </c>
       <c r="B4" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>130433152</v>
       </c>
       <c r="B5" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130433143</v>
       </c>
       <c r="B6" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,42 +1895,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130433118</v>
+        <v>130433110</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>111183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>360679</v>
+        <v>360682</v>
       </c>
       <c r="R12" t="n">
-        <v>6540844</v>
+        <v>6540850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,32 +1987,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2030,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130433110</v>
+        <v>130433111</v>
       </c>
       <c r="B13" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360682</v>
+        <v>360659</v>
       </c>
       <c r="R13" t="n">
-        <v>6540850</v>
+        <v>6540849</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,42 +2127,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130433111</v>
+        <v>130433118</v>
       </c>
       <c r="B14" t="n">
-        <v>111145</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2189,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>360659</v>
+        <v>360679</v>
       </c>
       <c r="R14" t="n">
-        <v>6540849</v>
+        <v>6540844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Rejäla äldre hackspår på ca 2-3 meters höjd i en grov levande gran i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,13 +2219,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130433106</v>
+        <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>111145</v>
+        <v>101191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>360736</v>
+        <v>360629</v>
       </c>
       <c r="R15" t="n">
-        <v>6540885</v>
+        <v>6540915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130433157</v>
+        <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>101177</v>
+        <v>111183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>360629</v>
+        <v>360736</v>
       </c>
       <c r="R16" t="n">
-        <v>6540915</v>
+        <v>6540885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,7 +2497,7 @@
         <v>130433100</v>
       </c>
       <c r="B17" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433144</v>
+        <v>130433108</v>
       </c>
       <c r="B18" t="n">
-        <v>101177</v>
+        <v>111183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360645</v>
+        <v>360696</v>
       </c>
       <c r="R18" t="n">
-        <v>6540823</v>
+        <v>6540881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,10 +2726,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130433161</v>
+        <v>130433144</v>
       </c>
       <c r="B19" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>360670</v>
+        <v>360645</v>
       </c>
       <c r="R19" t="n">
-        <v>6540973</v>
+        <v>6540823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2805,6 +2805,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130433108</v>
+        <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>111145</v>
+        <v>101191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2880,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>360696</v>
+        <v>360670</v>
       </c>
       <c r="R20" t="n">
-        <v>6540881</v>
+        <v>6540973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2916,11 +2921,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,7 +2956,7 @@
         <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>130433159</v>
       </c>
       <c r="B23" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>130433101</v>
       </c>
       <c r="B24" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>130433105</v>
       </c>
       <c r="B25" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>130433155</v>
       </c>
       <c r="B26" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3666,10 +3666,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433102</v>
+        <v>130433149</v>
       </c>
       <c r="B27" t="n">
-        <v>111145</v>
+        <v>101191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360627</v>
+        <v>360769</v>
       </c>
       <c r="R27" t="n">
-        <v>6540799</v>
+        <v>6540905</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433149</v>
+        <v>130433102</v>
       </c>
       <c r="B28" t="n">
-        <v>101177</v>
+        <v>111183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360769</v>
+        <v>360627</v>
       </c>
       <c r="R28" t="n">
-        <v>6540905</v>
+        <v>6540799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433103</v>
+        <v>130433160</v>
       </c>
       <c r="B35" t="n">
-        <v>111145</v>
+        <v>101191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360640</v>
+        <v>360656</v>
       </c>
       <c r="R35" t="n">
-        <v>6540794</v>
+        <v>6540928</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,11 +4688,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4725,10 +4720,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130433160</v>
+        <v>130433147</v>
       </c>
       <c r="B36" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,10 +4763,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>360656</v>
+        <v>360645</v>
       </c>
       <c r="R36" t="n">
-        <v>6540928</v>
+        <v>6540790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4804,6 +4799,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433147</v>
+        <v>130433103</v>
       </c>
       <c r="B37" t="n">
-        <v>101177</v>
+        <v>111183</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360645</v>
+        <v>360640</v>
       </c>
       <c r="R37" t="n">
-        <v>6540790</v>
+        <v>6540794</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5078,7 +5078,7 @@
         <v>130433153</v>
       </c>
       <c r="B39" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 61156-2025 artfynd.xlsx
+++ b/artfynd/A 61156-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130433120</v>
       </c>
       <c r="B3" t="n">
-        <v>58236</v>
+        <v>58250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130433151</v>
+        <v>130433143</v>
       </c>
       <c r="B4" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360741</v>
+        <v>360644</v>
       </c>
       <c r="R4" t="n">
-        <v>6540886</v>
+        <v>6540876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130433152</v>
+        <v>130433151</v>
       </c>
       <c r="B5" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360683</v>
+        <v>360741</v>
       </c>
       <c r="R5" t="n">
-        <v>6540849</v>
+        <v>6540886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkbarrskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130433143</v>
+        <v>130433152</v>
       </c>
       <c r="B6" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360644</v>
+        <v>360683</v>
       </c>
       <c r="R6" t="n">
-        <v>6540876</v>
+        <v>6540849</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>Vintergröna blad i äldre kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
         <v>130433115</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>57875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>130433116</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>57875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>130433109</v>
       </c>
       <c r="B9" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>130433146</v>
       </c>
       <c r="B10" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>130433113</v>
       </c>
       <c r="B11" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>130433110</v>
       </c>
       <c r="B12" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>130433111</v>
       </c>
       <c r="B13" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>130433118</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>57875</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>130433157</v>
       </c>
       <c r="B15" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>130433106</v>
       </c>
       <c r="B16" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130433100</v>
+        <v>130433108</v>
       </c>
       <c r="B17" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>360646</v>
+        <v>360696</v>
       </c>
       <c r="R17" t="n">
-        <v>6540820</v>
+        <v>6540881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130433108</v>
+        <v>130433100</v>
       </c>
       <c r="B18" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>360696</v>
+        <v>360646</v>
       </c>
       <c r="R18" t="n">
-        <v>6540881</v>
+        <v>6540820</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Vintergröna blad på marken i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,7 +2729,7 @@
         <v>130433144</v>
       </c>
       <c r="B19" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130433161</v>
       </c>
       <c r="B20" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>130433145</v>
       </c>
       <c r="B21" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>130433098</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58037</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130433159</v>
+        <v>130433105</v>
       </c>
       <c r="B23" t="n">
-        <v>101191</v>
+        <v>111197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>360652</v>
+        <v>360726</v>
       </c>
       <c r="R23" t="n">
-        <v>6540954</v>
+        <v>6540873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
         <v>130433101</v>
       </c>
       <c r="B24" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130433105</v>
+        <v>130433159</v>
       </c>
       <c r="B25" t="n">
-        <v>111183</v>
+        <v>101205</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,21 +3440,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>360726</v>
+        <v>360652</v>
       </c>
       <c r="R25" t="n">
-        <v>6540873</v>
+        <v>6540954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
+          <t>Växer på nederdel av brant klippyta i brant med gammal granskog med asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130433155</v>
+        <v>130433102</v>
       </c>
       <c r="B26" t="n">
-        <v>101191</v>
+        <v>111197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>360610</v>
+        <v>360627</v>
       </c>
       <c r="R26" t="n">
-        <v>6540895</v>
+        <v>6540799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I äldre granskog nedanför en brant.</t>
+          <t>Vintergröna blad i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,11 +3644,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3666,10 +3661,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130433149</v>
+        <v>130433155</v>
       </c>
       <c r="B27" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>360769</v>
+        <v>360610</v>
       </c>
       <c r="R27" t="n">
-        <v>6540905</v>
+        <v>6540895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>I äldre granskog nedanför en brant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,6 +3760,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130433102</v>
+        <v>130433149</v>
       </c>
       <c r="B28" t="n">
-        <v>111183</v>
+        <v>101205</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>360627</v>
+        <v>360769</v>
       </c>
       <c r="R28" t="n">
-        <v>6540799</v>
+        <v>6540905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Vintergröna blad i äldre kalkgranskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3901,7 +3901,7 @@
         <v>130433154</v>
       </c>
       <c r="B29" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>130433150</v>
       </c>
       <c r="B30" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130433112</v>
       </c>
       <c r="B31" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>130433099</v>
       </c>
       <c r="B32" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130433142</v>
       </c>
       <c r="B33" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>130433156</v>
       </c>
       <c r="B34" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130433160</v>
+        <v>130433103</v>
       </c>
       <c r="B35" t="n">
-        <v>101191</v>
+        <v>111197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>360656</v>
+        <v>360640</v>
       </c>
       <c r="R35" t="n">
-        <v>6540928</v>
+        <v>6540794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,6 +4688,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4723,7 +4728,7 @@
         <v>130433147</v>
       </c>
       <c r="B36" t="n">
-        <v>101191</v>
+        <v>101205</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4836,10 +4841,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130433103</v>
+        <v>130433160</v>
       </c>
       <c r="B37" t="n">
-        <v>111183</v>
+        <v>101205</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4847,21 +4852,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4879,10 +4884,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>360640</v>
+        <v>360656</v>
       </c>
       <c r="R37" t="n">
-        <v>6540794</v>
+        <v>6540928</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4915,11 +4920,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Både vintergröna blad och gamla fröställningar i äldre kalkgranskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4952,61 +4952,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130433117</v>
+        <v>130433153</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
+        <v>101205</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>360747</v>
+        <v>360657</v>
       </c>
       <c r="R38" t="n">
-        <v>6540846</v>
+        <v>6540844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5043,7 +5035,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
+          <t>I äldre granskog med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5052,6 +5044,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5075,53 +5068,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130433153</v>
+        <v>130433117</v>
       </c>
       <c r="B39" t="n">
-        <v>101191</v>
+        <v>57875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ormbergen öst, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>360657</v>
+        <v>360747</v>
       </c>
       <c r="R39" t="n">
-        <v>6540844</v>
+        <v>6540846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I äldre granskog med tydlig kalkpåverkan.</t>
+          <t>2 individer med lockläte i äldre granskog med inslag av asp och bitvis gott om stående död ved av gran. Hackspår efter spillkråka finns på flera platser i denna skog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5167,7 +5168,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>130433107</v>
       </c>
       <c r="B40" t="n">
-        <v>111183</v>
+        <v>111197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
